--- a/week-01/Ex5B_ResturantSurvey.xlsx
+++ b/week-01/Ex5B_ResturantSurvey.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kendratyler\Documents\dataanalytics\week-01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ABC7EC08-EA93-4532-B775-C2A7EA734475}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A602ACAE-5F83-4F27-BE5F-536828A94989}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3800" yWindow="1100" windowWidth="12530" windowHeight="10980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6580" yWindow="630" windowWidth="12530" windowHeight="10980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -118,6 +118,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="m/d/yyyy\ h:mm:ss"/>
+  </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -147,19 +150,26 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="9">
+  <dxfs count="10">
+    <dxf>
+      <numFmt numFmtId="165" formatCode="m/d/yyyy\ h:mm:ss"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
     <dxf>
@@ -179,9 +189,6 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -200,14 +207,14 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:K6" totalsRowShown="0">
   <autoFilter ref="A1:K6" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="8">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="1">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="id"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Start time">
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Start time" dataDxfId="0">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="startDate"/>
@@ -221,56 +228,56 @@
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Email" dataDxfId="7">
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Email" dataDxfId="9">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="responder"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Name" dataDxfId="6">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Name" dataDxfId="8">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="responderName"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="How would you rate your overall dining experience at Vapiano today?" dataDxfId="5">
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="How would you rate your overall dining experience at Vapiano today?" dataDxfId="7">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r34fd02c3acb5481d96350d80a2f60b29"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="How would you rate the cleanliness of the restaurant?" dataDxfId="4">
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="How would you rate the cleanliness of the restaurant?" dataDxfId="6">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r00e14d79202b499d8e58442ca7b2dec1"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="How often do you Visit ?" dataDxfId="3">
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="How often do you Visit ?" dataDxfId="5">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="refde9f051aff467f9332028dea498d36"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Do you feel you received good value for your money?" dataDxfId="2">
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Do you feel you received good value for your money?" dataDxfId="4">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="radb5580a6a1448c59fe80c8beb172cde"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Did staff members greet you in a friendly and welcoming manner?" dataDxfId="1">
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Did staff members greet you in a friendly and welcoming manner?" dataDxfId="3">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r3f66d0aa1e794b7ebc82cc8edda152ed"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="How likely are you to recommend Vapiano to a friend or family member?_x000a_" dataDxfId="0">
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="How likely are you to recommend Vapiano to a friend or family member?_x000a_" dataDxfId="2">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r7cbd19c7b7924416a2b14adcac1d9bee"/>
@@ -606,7 +613,7 @@
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
@@ -642,7 +649,7 @@
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2" s="3">
         <v>46122.116377314815</v>
       </c>
       <c r="C2" s="1">
@@ -677,7 +684,7 @@
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3" s="3">
         <v>46122.360289351855</v>
       </c>
       <c r="C3" s="1">
@@ -712,7 +719,7 @@
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4" s="3">
         <v>46122.474317129629</v>
       </c>
       <c r="C4" s="1">
@@ -747,7 +754,7 @@
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5" s="3">
         <v>46122.518923611111</v>
       </c>
       <c r="C5" s="1">
@@ -782,7 +789,7 @@
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B6" s="3">
         <v>46122.867280092592</v>
       </c>
       <c r="C6" s="1">
